--- a/Results/df_mnd_lica_pla_sequential_trial_gap_unweighted.xlsx
+++ b/Results/df_mnd_lica_pla_sequential_trial_gap_unweighted.xlsx
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="E2" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="G2" t="n">
-        <v>1.712692879599123e-06</v>
+        <v>1.150847023462774e-08</v>
       </c>
     </row>
     <row r="3">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="E3" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="F3" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="G3" t="n">
-        <v>6.449171834259952e-07</v>
+        <v>3.82176101144642e-09</v>
       </c>
     </row>
     <row r="4">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.338955559316828e-07</v>
+        <v>7.512897350522418e-10</v>
       </c>
     </row>
     <row r="5">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="E5" t="n">
         <v>0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="G5" t="n">
-        <v>7.306341392800647e-07</v>
+        <v>1.359094222805859e-07</v>
       </c>
     </row>
   </sheetData>
